--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74197490</v>
+        <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>57813</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100136</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djurholmen, Sk</t>
+          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380056</v>
+        <v>380073</v>
       </c>
       <c r="R2" t="n">
-        <v>6246788</v>
+        <v>6246782</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sedd av Wanja Zeilon och Fredrik Broberg.</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,30 +763,734 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494590</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74197490</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurholmen, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>380056</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6246788</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sedd av Wanja Zeilon och Fredrik Broberg.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74197490</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136494442</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58165</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hässlebo våt sänka, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>380119</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6246628</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494442</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136494475</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58165</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>380239</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6246730</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494475</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136494585</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56935</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kulle med stenblock, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>380073</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6246782</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494585</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136494463</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98203</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hässlebo slänt, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>380239</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6246730</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494463</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136494826</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98203</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bokbacke, Djurholmamossen, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>379956</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6246688</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåssjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136494826</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35675-2026 artfynd.xlsx
+++ b/artfynd/A 35675-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136494590</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>136494463</v>
       </c>
       <c r="B7" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>136494826</v>
       </c>
       <c r="B8" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
